--- a/游戏设计王/老虎机数学专题-扩展百搭.xlsx
+++ b/游戏设计王/老虎机数学专题-扩展百搭.xlsx
@@ -456,12 +456,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000%"/>
+    <numFmt numFmtId="177" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -1166,7 +1167,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1228,6 +1229,11 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -11299,7 +11305,7 @@
         <f>I43*I44*I45*I46*I47</f>
         <v>1536</v>
       </c>
-      <c r="E70" s="11">
+      <c r="E70" s="33">
         <f>(B70*B32+C70*C32+D70*D32)/POWER(20,5)</f>
         <v>0.1536</v>
       </c>
@@ -11359,7 +11365,7 @@
         <f>J43*J44*J45*J46*J47</f>
         <v>1792</v>
       </c>
-      <c r="E71" s="11">
+      <c r="E71" s="33">
         <f>(B71*B33+C71*C33+D71*D33)/POWER(20,5)</f>
         <v>0.168</v>
       </c>
@@ -11419,7 +11425,7 @@
         <f>K43*K44*K45*K46*K47</f>
         <v>1792</v>
       </c>
-      <c r="E72" s="11">
+      <c r="E72" s="33">
         <f>(B72*B34+C72*C34+D72*D34)/POWER(20,5)</f>
         <v>0.1428</v>
       </c>
@@ -11479,7 +11485,7 @@
         <f>L43*L44*L45*L46*L47</f>
         <v>1536</v>
       </c>
-      <c r="E73" s="11">
+      <c r="E73" s="33">
         <f>(B73*B35+C73*C35+D73*D35)/POWER(20,5)</f>
         <v>0.1224</v>
       </c>
@@ -11539,7 +11545,7 @@
         <f>M43*M44*M45*M46*M47</f>
         <v>1536</v>
       </c>
-      <c r="E74" s="11">
+      <c r="E74" s="33">
         <f>(B74*B36+C74*C36+D74*D36)/POWER(20,5)</f>
         <v>0.0912</v>
       </c>
@@ -11596,7 +11602,7 @@
       <c r="D75" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E75" s="12">
+      <c r="E75" s="34">
         <f>SUM(E70:E74)</f>
         <v>0.678</v>
       </c>
@@ -11824,7 +11830,7 @@
         <f>I51*I52*I53*I54*I55</f>
         <v>1792</v>
       </c>
-      <c r="E79" s="11">
+      <c r="E79" s="33">
         <f>(B79*B32+C79*C32+D79*D32)/POWER(20,5)</f>
         <v>0.1792</v>
       </c>
@@ -11884,7 +11890,7 @@
         <f>J51*J52*J53*J54*J55</f>
         <v>1792</v>
       </c>
-      <c r="E80" s="11">
+      <c r="E80" s="33">
         <f>(B80*B33+C80*C33+D80*D33)/POWER(20,5)</f>
         <v>0.168</v>
       </c>
@@ -11944,7 +11950,7 @@
         <f>K51*K52*K53*K54*K55</f>
         <v>1536</v>
       </c>
-      <c r="E81" s="11">
+      <c r="E81" s="33">
         <f>(B81*B34+C81*C34+D81*D34)/POWER(20,5)</f>
         <v>0.1224</v>
       </c>
@@ -12004,7 +12010,7 @@
         <f>L51*L52*L53*L54*L55</f>
         <v>1536</v>
       </c>
-      <c r="E82" s="11">
+      <c r="E82" s="33">
         <f>(B82*B35+C82*C35+D82*D35)/POWER(20,5)</f>
         <v>0.1224</v>
       </c>
@@ -12064,7 +12070,7 @@
         <f>M51*M52*M53*M54*M55</f>
         <v>1536</v>
       </c>
-      <c r="E83" s="11">
+      <c r="E83" s="33">
         <f>(B83*B36+C83*C36+D83*D36)/POWER(20,5)</f>
         <v>0.0912</v>
       </c>
@@ -12121,7 +12127,7 @@
       <c r="D84" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E84" s="12">
+      <c r="E84" s="34">
         <f>SUM(E79:E83)</f>
         <v>0.6832</v>
       </c>
@@ -12349,7 +12355,7 @@
         <f>I59*I60*I61*I62*I63</f>
         <v>1536</v>
       </c>
-      <c r="E88" s="11">
+      <c r="E88" s="33">
         <f>(B88*B32+C88*C32+D88*D32)/POWER(20,5)</f>
         <v>0.1536</v>
       </c>
@@ -12409,7 +12415,7 @@
         <f>J59*J60*J61*J62*J63</f>
         <v>1536</v>
       </c>
-      <c r="E89" s="11">
+      <c r="E89" s="33">
         <f>(B89*B33+C89*C33+D89*D33)/POWER(20,5)</f>
         <v>0.144</v>
       </c>
@@ -12469,7 +12475,7 @@
         <f>K59*K60*K61*K62*K63</f>
         <v>1792</v>
       </c>
-      <c r="E90" s="11">
+      <c r="E90" s="33">
         <f>(B90*B34+C90*C34+D90*D34)/POWER(20,5)</f>
         <v>0.1428</v>
       </c>
@@ -12529,7 +12535,7 @@
         <f>L59*L60*L61*L62*L63</f>
         <v>1792</v>
       </c>
-      <c r="E91" s="11">
+      <c r="E91" s="33">
         <f>(B91*B35+C91*C35+D91*D35)/POWER(20,5)</f>
         <v>0.1428</v>
       </c>
@@ -12589,7 +12595,7 @@
         <f>M59*M60*M61*M62*M63</f>
         <v>1536</v>
       </c>
-      <c r="E92" s="11">
+      <c r="E92" s="33">
         <f>(B92*B36+C92*C36+D92*D36)/POWER(20,5)</f>
         <v>0.0912</v>
       </c>
@@ -12646,7 +12652,7 @@
       <c r="D93" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E93" s="12">
+      <c r="E93" s="34">
         <f>SUM(E88:E92)</f>
         <v>0.6744</v>
       </c>
@@ -12918,7 +12924,7 @@
       <c r="A98" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B98" s="13">
+      <c r="B98" s="35">
         <f>E75</f>
         <v>0.678</v>
       </c>
@@ -12975,7 +12981,7 @@
       <c r="A99" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B99" s="11">
+      <c r="B99" s="33">
         <f>E84</f>
         <v>0.6832</v>
       </c>
@@ -13032,7 +13038,7 @@
       <c r="A100" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B100" s="11">
+      <c r="B100" s="33">
         <f>E93</f>
         <v>0.6744</v>
       </c>
@@ -13145,7 +13151,7 @@
       <c r="A102" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B102" s="12">
+      <c r="B102" s="34">
         <f>AVERAGE(B98:B100)</f>
         <v>0.678533333333333</v>
       </c>
